--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562757632</v>
+        <v>46157.93073733377</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93073733377</v>
+        <v>46157.93155965899</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93155965899</v>
+        <v>46157.93394432323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394432323</v>
+        <v>46157.93709995777</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709995777</v>
+        <v>46158.28211364913</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211364913</v>
+        <v>46158.29667223406</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29667223406</v>
+        <v>46158.29806750415</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806750415</v>
+        <v>46158.33382179141</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382179141</v>
+        <v>46158.36849400486</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36849400486</v>
+        <v>46158.37282315509</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
